--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-06T08:28:50+00:00</t>
+          <t>2026-09-07T09:06:20+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-07T09:06:20+00:00</t>
+          <t>2026-09-08T08:44:11+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-08T08:44:11+00:00</t>
+          <t>2026-09-09T08:49:35+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-09T08:49:35+00:00</t>
+          <t>2026-09-10T08:48:16+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-10T08:48:16+00:00</t>
+          <t>2026-09-11T08:45:16+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-11T08:45:16+00:00</t>
+          <t>2026-09-12T08:30:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-12T08:30:01+00:00</t>
+          <t>2026-09-13T09:17:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-13T09:17:01+00:00</t>
+          <t>2026-09-14T09:41:29+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-14T09:41:29+00:00</t>
+          <t>2026-09-15T09:17:26+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-15T09:17:26+00:00</t>
+          <t>2026-09-16T09:10:45+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-16T09:10:45+00:00</t>
+          <t>2026-09-17T09:18:23+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-17T09:18:23+00:00</t>
+          <t>2026-09-18T08:53:54+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-18T08:53:54+00:00</t>
+          <t>2026-09-19T08:40:20+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-19T08:40:20+00:00</t>
+          <t>2026-09-20T09:09:49+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-20T09:09:49+00:00</t>
+          <t>2026-09-21T09:45:56+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-21T09:45:56+00:00</t>
+          <t>2026-09-22T09:10:11+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-22T09:10:11+00:00</t>
+          <t>2026-09-23T09:10:54+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-23T09:10:54+00:00</t>
+          <t>2026-09-24T09:08:41+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-24T09:08:41+00:00</t>
+          <t>2026-09-25T09:28:38+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-25T09:28:38+00:00</t>
+          <t>2026-09-26T09:13:48+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-26T09:13:48+00:00</t>
+          <t>2026-09-27T09:53:43+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-27T09:53:43+00:00</t>
+          <t>2026-09-28T10:42:15+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:15+00:00</t>
+          <t>2026-09-29T10:29:57+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-29T10:29:57+00:00</t>
+          <t>2026-09-30T10:21:19+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-09-30T10:21:19+00:00</t>
+          <t>2026-10-01T10:47:57+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-01T10:47:57+00:00</t>
+          <t>2026-10-02T10:22:29+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-02T10:22:29+00:00</t>
+          <t>2026-10-03T09:44:15+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-03T09:44:15+00:00</t>
+          <t>2026-10-04T10:28:09+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-04T10:28:09+00:00</t>
+          <t>2026-10-05T11:16:44+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-05T11:16:44+00:00</t>
+          <t>2026-10-06T11:06:23+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-06T11:06:23+00:00</t>
+          <t>2026-10-07T10:55:23+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-07T10:55:23+00:00</t>
+          <t>2026-10-08T11:12:40+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-08T11:12:40+00:00</t>
+          <t>2026-10-09T11:11:25+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-09T11:11:25+00:00</t>
+          <t>2026-10-10T10:28:51+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-10T10:28:51+00:00</t>
+          <t>2026-10-11T10:40:50+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-11T10:40:50+00:00</t>
+          <t>2026-10-12T11:45:28+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-12T11:45:28+00:00</t>
+          <t>2026-10-13T11:32:14+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-13T11:32:14+00:00</t>
+          <t>2026-10-14T09:22:06+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-14T09:22:06+00:00</t>
+          <t>2026-10-15T09:00:07+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-15T09:00:07+00:00</t>
+          <t>2026-10-16T08:51:34+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-16T08:51:34+00:00</t>
+          <t>2026-10-17T08:22:20+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-17T08:22:20+00:00</t>
+          <t>2026-10-18T08:42:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-18T08:42:01+00:00</t>
+          <t>2026-10-19T09:42:56+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-19T09:42:56+00:00</t>
+          <t>2026-10-20T09:16:41+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-20T09:16:41+00:00</t>
+          <t>2026-10-21T09:13:28+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-21T09:13:28+00:00</t>
+          <t>2026-10-22T09:16:05+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-22T09:16:05+00:00</t>
+          <t>2026-10-23T09:11:52+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-23T09:11:52+00:00</t>
+          <t>2026-10-24T08:45:22+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-24T08:45:22+00:00</t>
+          <t>2026-10-25T09:01:08+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-25T09:01:08+00:00</t>
+          <t>2026-10-26T09:54:50+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-26T09:54:50+00:00</t>
+          <t>2026-10-27T09:40:53+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-27T09:40:53+00:00</t>
+          <t>2026-10-28T10:25:39+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-28T10:25:39+00:00</t>
+          <t>2026-10-29T10:46:01+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-29T10:46:01+00:00</t>
+          <t>2026-10-30T10:45:30+00:00</t>
         </is>
       </c>
     </row>

--- a/build/events_master.xlsx
+++ b/build/events_master.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2026-10-30T10:45:30+00:00</t>
+          <t>2026-10-31T10:14:53+00:00</t>
         </is>
       </c>
     </row>
